--- a/apps/api/assets/vocabulary/初中/人教版/人教版初中英语八年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/人教版/人教版初中英语八年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D464"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -690,6 +690,16 @@
           <t>of course</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 当然
@@ -974,6 +984,16 @@
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>feel like</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1231,6 +1251,16 @@
           <t>because of</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 因
@@ -1410,6 +1440,16 @@
           <t>Central Park</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 中央公园；纽约中央公园；中心公园</t>
@@ -1422,6 +1462,16 @@
           <t>Huangguoshu Waterfall</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1434,6 +1484,16 @@
           <t>Hong Kong</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 香港
@@ -1514,6 +1574,16 @@
           <t>Weld Quay</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1526,6 +1596,16 @@
           <t>Penang Hill</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -1538,6 +1618,16 @@
           <t>Tian'anmen Square</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 天安门广场；周年联欢晚会；天安门广场夜景</t>
@@ -1548,6 +1638,16 @@
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>the Palace Museum</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1654,6 +1754,16 @@
           <t>hardly ever</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 难得；很少
@@ -1810,6 +1920,16 @@
           <t>swing dance</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 摇摆舞；摇摆舞蹈；於摇摆舞</t>
@@ -1869,6 +1989,16 @@
           <t>at least</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 至少
@@ -2018,6 +2148,16 @@
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>per cent</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2525,6 +2665,16 @@
           <t>Claire</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
           <t>n. 克莱儿（女子名）</t>
@@ -2559,6 +2709,16 @@
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>American Teenager</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -2899,6 +3059,16 @@
           <t>care about</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 在意
@@ -2983,6 +3153,16 @@
           <t>as long as</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">conj. 只要
@@ -3018,6 +3198,16 @@
       <c r="A119" s="2" t="inlineStr">
         <is>
           <t>be different from</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -3059,6 +3249,16 @@
           <t>bring out</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 公布；说出；出版；上演
@@ -3119,6 +3319,16 @@
           <t>the same as</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 与…同样
@@ -3274,6 +3484,16 @@
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>in fact</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -3434,6 +3654,16 @@
           <t>be similar to</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 像
@@ -3470,6 +3700,16 @@
           <t>primary school</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 小学
@@ -3547,6 +3787,16 @@
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Nelly</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -3885,6 +4135,16 @@
           <t>so far</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 就是那么些；到现在为止；到目前(此地)为止；就此范围来说
@@ -4154,6 +4414,16 @@
           <t>have ... in common</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 没有共同之处；有某些共同之处
@@ -4189,6 +4459,16 @@
           <t>all kinds of</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 种种
@@ -4224,6 +4504,16 @@
           <t>be up to</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 面对；在干；居心
@@ -4258,6 +4548,16 @@
       <c r="A177" s="2" t="inlineStr">
         <is>
           <t>play a role</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -4456,6 +4756,16 @@
           <t>take ... seriously</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 重视；认真(想)；当真
@@ -4517,6 +4827,16 @@
           <t>Greg</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
           <t>n. 格雷格（男子名，等于Gregory）</t>
@@ -4529,6 +4849,16 @@
           <t>Depp</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
           <t>n. 德普（姓氏）</t>
@@ -4541,6 +4871,16 @@
           <t>Danny</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
           <t>n. 手（尤用于与幼儿说话时）；侦察用车</t>
@@ -4620,6 +4960,16 @@
           <t>American Idol</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 美国偶像；美国偶像大赛；美国偶像最终决赛</t>
@@ -4632,6 +4982,16 @@
           <t>America's Got Talent</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -4642,6 +5002,16 @@
       <c r="A197" s="2" t="inlineStr">
         <is>
           <t>China's Got Talent</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -4794,6 +5164,16 @@
       <c r="A204" s="2" t="inlineStr">
         <is>
           <t>find out</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -5414,6 +5794,16 @@
           <t>be ready to</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 准备好；准备做某事；预备</t>
@@ -5497,6 +5887,16 @@
           <t>take sb.'s place</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 解构发生；就位</t>
@@ -5531,6 +5931,16 @@
           <t>do a good job</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 好好干；干得好；干得很好</t>
@@ -5565,6 +5975,16 @@
           <t>Walt Disney</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 迪士尼；华特迪士尼；迪斯尼</t>
@@ -5577,6 +5997,16 @@
           <t>Minnie</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
           <t>n. 迫击炮
@@ -5590,6 +6020,16 @@
           <t>Mickey Mouse</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 米老鼠；分掷炸弹的装置；〈美俚〉【军】多余或无关重要的东西
@@ -5604,6 +6044,16 @@
           <t>Steamboat Willie</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -5638,6 +6088,16 @@
           <t>the Hollywood Walk of Fame</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -5671,6 +6131,16 @@
       <c r="A246" s="2" t="inlineStr">
         <is>
           <t>computer programmer</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -5873,6 +6343,16 @@
           <t>be sure about</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 就象…一样地不容怀疑。；把握
@@ -6161,6 +6641,16 @@
           <t>be able to</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 能够
@@ -6291,6 +6781,16 @@
           <t>at the beginning of</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 前奏；处于…的开端；起初
@@ -6393,6 +6893,16 @@
       <c r="A279" s="2" t="inlineStr">
         <is>
           <t>have to do with</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -6543,6 +7053,16 @@
       <c r="A286" s="2" t="inlineStr">
         <is>
           <t>agree with</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -6629,6 +7149,16 @@
           <t>Andy</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
           <t>n. 安迪（男子名，等于Andrew）</t>
@@ -6641,6 +7171,16 @@
           <t>Ken</t>
         </is>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
           <t>n. 视野范围，见地，知识范围</t>
@@ -6695,6 +7235,16 @@
       <c r="A294" s="2" t="inlineStr">
         <is>
           <t>The Old Man and the Sea</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -6946,6 +7496,16 @@
           <t>play a part</t>
         </is>
       </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 扮演…角色；假装
@@ -7256,6 +7816,16 @@
       <c r="A319" s="2" t="inlineStr">
         <is>
           <t>over and over again</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -7342,6 +7912,16 @@
           <t>hundreds of</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 好几百
@@ -7406,6 +7986,16 @@
           <t>fall down</t>
         </is>
       </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (向下游)流下；〔美俚〕失败；跌倒；同“fall”
@@ -7678,6 +8268,16 @@
           <t>White</t>
         </is>
       </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
           <t>n. 白色；洁白；白种人
@@ -7713,6 +8313,16 @@
       <c r="A340" s="2" t="inlineStr">
         <is>
           <t>milk shake</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -8294,6 +8904,16 @@
           <t>Thanksgiving</t>
         </is>
       </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
           <t>n. 感恩</t>
@@ -8657,6 +9277,16 @@
           <t>prepare for</t>
         </is>
       </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 准备；为…作准备；为…做准备</t>
@@ -8734,6 +9364,16 @@
       <c r="A385" s="2" t="inlineStr">
         <is>
           <t>another time</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -8914,6 +9554,16 @@
           <t>the day before yesterday</t>
         </is>
       </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 前天
@@ -8927,6 +9577,16 @@
           <t>the day after tomorrow</t>
         </is>
       </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 后天
@@ -9005,6 +9665,16 @@
       <c r="A398" s="2" t="inlineStr">
         <is>
           <t>turn down</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
@@ -9162,6 +9832,16 @@
           <t>take a trip</t>
         </is>
       </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 旅行
@@ -9291,6 +9971,16 @@
           <t>look forward to</t>
         </is>
       </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 盼望
@@ -9302,6 +9992,16 @@
       <c r="A412" s="2" t="inlineStr">
         <is>
           <t>hear from</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
@@ -9503,6 +10203,16 @@
           <t>Ted</t>
         </is>
       </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
           <t>vt. 翻晒</t>
@@ -9513,6 +10223,16 @@
       <c r="A422" s="2" t="inlineStr">
         <is>
           <t>Vince</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -9662,6 +10382,16 @@
       <c r="A429" s="2" t="inlineStr">
         <is>
           <t>potato chips</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
@@ -9845,6 +10575,16 @@
           <t>keep ... to oneself</t>
         </is>
       </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 强调；紧贴；秘而不宣；独自承受
@@ -10250,6 +10990,16 @@
           <t>in half</t>
         </is>
       </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 成两半
@@ -10332,6 +11082,16 @@
           <t>Ben</t>
         </is>
       </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
           <t>n. 本（男子名）；（苏格兰）内室</t>
@@ -10386,6 +11146,16 @@
       <c r="A462" s="2" t="inlineStr">
         <is>
           <t>Mills</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
